--- a/results/job_matches_2026-06-24.xlsx
+++ b/results/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fervo Energy</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0394f69da3f3e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=039085eefda4910b</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039085eefda4910b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0ab289cd7fe039</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0ab289cd7fe039</t>
+          <t>https://www.indeed.com/viewjob?jk=419482d1afcd3dfa</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419482d1afcd3dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e0aa784e6be257</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e0aa784e6be257</t>
+          <t>https://www.indeed.com/viewjob?jk=161d68a146e54847</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=161d68a146e54847</t>
+          <t>https://www.indeed.com/viewjob?jk=de651327871de2a3</t>
         </is>
       </c>
     </row>
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de651327871de2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=10fc8879f0cc99f4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
+          <t>https://www.indeed.com/viewjob?jk=bbb3b596dc7fb790</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hadoop Big Data Developer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29e6310605d49253</t>
+          <t>https://www.indeed.com/viewjob?jk=f93edc3cecf59f63</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hadoop Big Data Developer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc88bcb51e44d51a</t>
+          <t>https://www.indeed.com/viewjob?jk=19ea0d6a1b2e3218</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fc8879f0cc99f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8809bbf8ab7927af</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbb3b596dc7fb790</t>
+          <t>https://www.indeed.com/viewjob?jk=323c9080a1c5fd3c</t>
         </is>
       </c>
     </row>
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93edc3cecf59f63</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbeaab23e615686</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ea0d6a1b2e3218</t>
+          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809bbf8ab7927af</t>
+          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Data Engineer - AWS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323c9080a1c5fd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e78104b24dec2f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbeaab23e615686</t>
+          <t>https://www.indeed.com/viewjob?jk=f2808323837e75ba</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>Lambda, RDS, Azure, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
+          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e78104b24dec2f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f587376655a4150</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
+          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Senior Data Engineer – Insurance Data Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CCMSI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Danville, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3882ec5294241cd4</t>
+          <t>https://www.indeed.com/viewjob?jk=db60959b33c4c354</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Senior Data Engineer – Insurance Data Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CCMSI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Danville, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2808323837e75ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bc118c13047230ec</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0995774c98d8f64</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f17df007528af5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Insurance Data Platform</t>
+          <t>Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CCMSI</t>
+          <t>ClearpointCo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Danville, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc118c13047230ec</t>
+          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,137 +1371,137 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
+          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ab8a36f01bb8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=98afda0b4cf6550d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Technical Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, Databricks, Hadoop, HDFS, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82ecb174d2653ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ClearpointCo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc54ae940e4cedd7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e829f800cb4fc94c</t>
+          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
+          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer – Consumer Fraud Engineering - FDP</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, ECS, RDS, Scala, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ab4e0da5923841</t>
+          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Motley Fool</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0db552d42bcff54</t>
+          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Technical Architect</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
+          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Scala, Oracle, MySQL, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10028e1c2f1ec5b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analyst Databricks</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
+          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Site Reliability / DevOps Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
+          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
+          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Databricks Architect with P&amp;C</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Michigan City, IN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Spark, PySpark, Scala, Kafka, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2920f81c9f2b0e5</t>
+          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Public Media</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
+          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Contingent</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CRYOPORT SYSTEMS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
+          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Franciscan Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mishawaka, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
+          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Developer - PEGA Platform</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a302dc9c31a0f30</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Authentication</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, GCP, Scala, MySQL, DynamoDB, MLOps</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfb62e4da91a70a</t>
+          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
+          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e718fc30d1d95fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Westwood, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,102 +2561,102 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e08fb2784687034</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39551869dd3c071</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4f85c793d08d00</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
+          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
+          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
+          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
+          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
+          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
+          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Agri -Tech - US</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sun World International, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4091f0c081992e7e</t>
+          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,137 +3016,137 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer - Fabric (100% Remote)</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ClearCaptions, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6333130bee69ff29</t>
+          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer, IT Software</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df6d60888f81ff6</t>
+          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Revelation Pharma</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3f72bf40c462ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7741fa0ff4bedb5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4f5a537d2c071e</t>
+          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Analyst Databricks</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
+          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Xai</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
+          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230f2097d39a709c</t>
+          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
         </is>
       </c>
     </row>
@@ -3308,20 +3308,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, Airflow</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cfab581c91ff74c</t>
+          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability / DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
+          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Full Stack Data Science Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Kafka, PostgreSQL, DynamoDB, CI/CD, Terraform</t>
+          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85eb25f65aeae0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
+          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>INTELLIGENCE APPLICATION DEVELOPER</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>University of Alabama, Birmingham</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,77 +3506,77 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6fbff522d2790e</t>
+          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
+          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9167fc909538321d</t>
+          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
         </is>
       </c>
     </row>
@@ -3588,160 +3588,160 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>American Public Media</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7920243ccd6b53ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer - Contingent</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>CRYOPORT SYSTEMS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ffe3a5ec1828269</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Applied Data Scientist / Machine Learning Engineer (Decision Intelligence)</t>
+          <t>Sr Software Developer - PEGA Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WorkWave™</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b9e5345cb308db2</t>
+          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer, Ads Product &amp; Tech</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Azure, GCP, Dataflow, Hadoop, Scala, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5c0a9a146a70778</t>
+          <t>https://www.indeed.com/viewjob?jk=59eacac00c3d239a</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>829 Studios</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
+          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data &amp; Integrations Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Alternate Solutions Health Network</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eedaa2000347db1</t>
+          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
+          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
+          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,19 +3926,19 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3947,11 +3947,11 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
+          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
+          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Business System Analyst</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, IAM, RDS, Databricks, Scala, Snowflake, Oracle, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598c10084371cc1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Engineer (Heavy backend/ AI-Assisted)</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8e641f619c036a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
+          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Technology Operations Consultant for QRM BSM</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Splunk, CI/CD, Terraform, SonarQube, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dfee75b9d636ca</t>
+          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Payments</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,67 +4171,67 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
+          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Cloud Systems Engineer</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Git, Datadog, Azure Monitor</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6aad263f77591b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Security Analyst</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
+          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
+          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
+          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
+          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
+          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Devops</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
+          <t>https://www.indeed.com/viewjob?jk=6dec79ae33f75455</t>
         </is>
       </c>
     </row>
@@ -4533,55 +4533,55 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Web Application Engineer (Irvine, US)</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>Xai</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
+          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9b6e8852617ed98</t>
+          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41be2609894619fb</t>
+          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Supervisor of Technical Product Development</t>
+          <t>Anaplan Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Murray, UT, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c39e750667d68b</t>
+          <t>https://www.indeed.com/viewjob?jk=8de2684c6f92101f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cloud Network Engineer II</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Amerisure</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98627ffbde1c523b</t>
+          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Associate DevOps Software Engineer</t>
+          <t>Sr. Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Keenfinity</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Fairport, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,59 +4766,59 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd7c7be3ac15aed</t>
+          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Systems Administrator/Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Common Objects</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Kafka, PostgreSQL, MongoDB, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b75462d74808ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior IT. SecDevOps Architect</t>
+          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Diverse Agile Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,17 +4826,822 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40347d597108dbff</t>
+          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Engineer 2</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EMCOR</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Tonawanda, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>829 Studios</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Cetera Financial Group</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Ascendion</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Data Security Analyst</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Web Application Engineer (Irvine, US)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Axon Networks</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Payments</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Cloud Network Engineer II</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Amerisure</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Farmington Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98627ffbde1c523b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-24.xlsx
+++ b/results/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python or GoLang Software Engineer - 2 days onsite (Chicago, IL) - FreeWheel</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
+          <t>https://www.indeed.com/viewjob?jk=2e805afd8491439b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
+          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e78104b24dec2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Data Engineer - AWS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2808323837e75ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e78104b24dec2f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
+          <t>https://www.indeed.com/viewjob?jk=f2808323837e75ba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>Lambda, RDS, Azure, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f587376655a4150</t>
+          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f587376655a4150</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Insurance Data Platform</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CCMSI</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Danville, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db60959b33c4c354</t>
+          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
         </is>
       </c>
     </row>
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc118c13047230ec</t>
+          <t>https://www.indeed.com/viewjob?jk=db60959b33c4c354</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer – Insurance Data Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>CCMSI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Danville, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f17df007528af5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc118c13047230ec</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ClearpointCo</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f17df007528af5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>ClearpointCo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
+          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Terraform)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98afda0b4cf6550d</t>
+          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Technical Architect</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
+          <t>https://www.indeed.com/viewjob?jk=98afda0b4cf6550d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Data Technical Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
+          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
+          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
+          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
+          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
+          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
+          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
+          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
+          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
+          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
+          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
+          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
+          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
+          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
+          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
+          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
+          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
+          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
+          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
+          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
+          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
+          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Analyst Databricks</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
+          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
+          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analyst Databricks</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Site Reliability / DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
+          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Data Science Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
+          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Site Reliability / DevOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
+          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Data Science Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Franciscan Health</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Mishawaka, IN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e2255548fb7bbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>American Public Media</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
+          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Contingent</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CRYOPORT SYSTEMS</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
+          <t>https://www.indeed.com/viewjob?jk=81ca06fa6ac3ac22</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr Software Developer - PEGA Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>American Public Media</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
+          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer, Ads Product &amp; Tech</t>
+          <t>Senior DevOps Engineer - Contingent</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>CRYOPORT SYSTEMS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Dataflow, Hadoop, Scala, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59eacac00c3d239a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Sr Software Developer - PEGA Platform</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
+          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
+          <t>Data Engineer, Ads Product &amp; Tech</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, EMR, Azure, GCP, Dataflow, Hadoop, Scala, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
+          <t>https://www.indeed.com/viewjob?jk=59eacac00c3d239a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
+          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
+          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
+          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
+          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
+          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
+          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
+          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
+          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
+          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
+          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer III Core Platform</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
+          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
+          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Databricks Devops</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dec79ae33f75455</t>
+          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
+          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Databricks Devops</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Xai</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6dec79ae33f75455</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>Xai</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
+          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Anaplan Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de2684c6f92101f</t>
+          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
+          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr. Developer</t>
+          <t>Anaplan Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
+          <t>https://www.indeed.com/viewjob?jk=8de2684c6f92101f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Developer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,42 +4791,42 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
+          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Manufacturing</t>
+          <t>ML Ops and Model accuracy Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,67 +4836,67 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de0ec3a9fcc76260</t>
+          <t>https://www.indeed.com/viewjob?jk=0b36b244637e89a0</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb0d50c9545da3ef</t>
+          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=537c1d9db4a843d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Senior Data Engineer - Austin, TX</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Trend Micro Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9c79f2bb16cdec7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5123,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Digital Engineering</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Vuori</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
+          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer, Digital Engineering</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Vuori</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
+          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
+          <t>https://www.indeed.com/viewjob?jk=8e26fb0df2e45c4d</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Security Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Web Application Engineer (Irvine, US)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Axon Networks</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c44451a9ac3ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Web Application Engineer (Irvine, US)</t>
+          <t>Senior Software Engineer, Payments</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
+          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Payments</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE)- Healthcare &amp; Life Sciences</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a6ad725be6599</t>
+          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Cloud Network Engineer II</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Amerisure</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5430,216 +5430,6 @@
         </is>
       </c>
       <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1e67e26f0646cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=993d9698a9b37218</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=82a2681ff687132c</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4e2d1576186543</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fbaa870dc0932a19</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cda2fa218c4511</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Cloud Network Engineer II</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Amerisure</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Farmington Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98627ffbde1c523b</t>
         </is>

--- a/results/job_matches_2026-06-24.xlsx
+++ b/results/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Automation Developer &amp; Data Scientist</t>
+          <t>Sr. Engineer, Data - Archimedes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.7</v>
+        <v>30.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, GCP, BigQuery</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8315a758255bb079</t>
+          <t>https://www.indeed.com/viewjob?jk=00efdae7133cac10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>29.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039085eefda4910b</t>
+          <t>https://www.indeed.com/viewjob?jk=06ac01a3b37b1411</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>AI Automation Developer &amp; Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>25.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0ab289cd7fe039</t>
+          <t>https://www.indeed.com/viewjob?jk=8315a758255bb079</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419482d1afcd3dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=039085eefda4910b</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e0aa784e6be257</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0ab289cd7fe039</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=161d68a146e54847</t>
+          <t>https://www.indeed.com/viewjob?jk=419482d1afcd3dfa</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de651327871de2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e0aa784e6be257</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fc8879f0cc99f4</t>
+          <t>https://www.indeed.com/viewjob?jk=161d68a146e54847</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbb3b596dc7fb790</t>
+          <t>https://www.indeed.com/viewjob?jk=de651327871de2a3</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93edc3cecf59f63</t>
+          <t>https://www.indeed.com/viewjob?jk=10fc8879f0cc99f4</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ea0d6a1b2e3218</t>
+          <t>https://www.indeed.com/viewjob?jk=bbb3b596dc7fb790</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809bbf8ab7927af</t>
+          <t>https://www.indeed.com/viewjob?jk=f93edc3cecf59f63</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323c9080a1c5fd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=19ea0d6a1b2e3218</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbeaab23e615686</t>
+          <t>https://www.indeed.com/viewjob?jk=8809bbf8ab7927af</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python or GoLang Software Engineer - 2 days onsite (Chicago, IL) - FreeWheel</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e805afd8491439b</t>
+          <t>https://www.indeed.com/viewjob?jk=323c9080a1c5fd3c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbeaab23e615686</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Python or GoLang Software Engineer - 2 days onsite (Chicago, IL) - FreeWheel</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e805afd8491439b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e78104b24dec2f</t>
+          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2808323837e75ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
+          <t>https://www.indeed.com/viewjob?jk=ea98351890cb41a5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Data Engineer - AWS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f587376655a4150</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e78104b24dec2f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>19.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
+          <t>https://www.indeed.com/viewjob?jk=849fb6429e007fcd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Insurance Data Platform</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CCMSI</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Danville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db60959b33c4c354</t>
+          <t>https://www.indeed.com/viewjob?jk=f2808323837e75ba</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Insurance Data Platform</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CCMSI</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Danville, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
+          <t>Lambda, RDS, Azure, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc118c13047230ec</t>
+          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f17df007528af5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f587376655a4150</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ClearpointCo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
+          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer – Insurance Data Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CCMSI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Danville, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
+          <t>https://www.indeed.com/viewjob?jk=db60959b33c4c354</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Terraform)</t>
+          <t>Senior Data Engineer – Insurance Data Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CCMSI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Danville, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98afda0b4cf6550d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc118c13047230ec</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Technical Architect</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f17df007528af5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ClearpointCo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
+          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
+          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,129 +1581,129 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
+          <t>https://www.indeed.com/viewjob?jk=98afda0b4cf6550d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
+          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
+          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Data Technical Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
+          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
+          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
+          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
+          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
+          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
+          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
+          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
+          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
+          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
+          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
+          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
+          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
+          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
+          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
+          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
+          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
+          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
+          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
+          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
+          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
+          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Analyst Databricks</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
+          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
+          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
         </is>
       </c>
     </row>
@@ -3378,20 +3378,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Site Reliability / DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,19 +3436,19 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
+          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Data Science Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3457,46 +3457,46 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
+          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
+          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
+          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Analyst Databricks</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ca06fa6ac3ac22</t>
+          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
         </is>
       </c>
     </row>
@@ -3658,20 +3658,20 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>American Public Media</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
+          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Contingent</t>
+          <t>Site Reliability / DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CRYOPORT SYSTEMS</t>
+          <t>eClerx</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
+          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,67 +3716,67 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
+          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Software Developer - PEGA Platform</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
+          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer, Ads Product &amp; Tech</t>
+          <t>Full Stack Data Science Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Dataflow, Hadoop, Scala, PostgreSQL, MySQL, DynamoDB</t>
+          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59eacac00c3d239a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
+          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
+          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
         </is>
       </c>
     </row>
@@ -3938,20 +3938,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
+          <t>https://www.indeed.com/viewjob?jk=81ca06fa6ac3ac22</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>American Public Media</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
+          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Senior DevOps Engineer - Contingent</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CRYOPORT SYSTEMS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Sr Software Developer - PEGA Platform</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
+          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Data Engineer, Ads Product &amp; Tech</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, Azure, GCP, Dataflow, Hadoop, Scala, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
+          <t>https://www.indeed.com/viewjob?jk=59eacac00c3d239a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
+          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
+          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
+          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
+          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
+          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
+          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer III Core Platform</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
+          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Databricks Devops</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dec79ae33f75455</t>
+          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
+          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Xai</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
+          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Anaplan Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de2684c6f92101f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr. Developer</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ML Ops and Model accuracy Engineer</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,67 +4836,67 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b36b244637e89a0</t>
+          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
+          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
+          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Austin, TX</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Trend Micro Inc.</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Engineer 2</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Xai</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
+          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EMCOR</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>829 Studios</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Anaplan Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,129 +5081,129 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
+          <t>https://www.indeed.com/viewjob?jk=8de2684c6f92101f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
+          <t>Sr. Developer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>endava</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
+          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Digital Engineering</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vuori</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
+          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer - Austin, TX</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Trend Micro Inc.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e26fb0df2e45c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Engineer 2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
+          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Web Application Engineer (Irvine, US)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>EMCOR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Payments</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>829 Studios</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
+          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Security Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Cetera Financial Group</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cloud Network Engineer II</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Amerisure</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,15 +5421,330 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, Digital Engineering</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Vuori</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform, SonarQube</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e26fb0df2e45c4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Ascendion</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Web Application Engineer (Irvine, US)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Axon Networks</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Payments</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Data Security Analyst</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Amentum</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Cloud Network Engineer II</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Amerisure</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Farmington Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
           <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98627ffbde1c523b</t>
         </is>

--- a/results/job_matches_2026-06-24.xlsx
+++ b/results/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,25 +1518,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34d52a48551c1790</t>
+          <t>https://www.indeed.com/viewjob?jk=98afda0b4cf6550d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Terraform)</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,24 +1571,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98afda0b4cf6550d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
+          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,59 +1651,59 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
+          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Data Technical Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Rysun labs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
+          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Technical Architect</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
+          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
+          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
+          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
+          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
+          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
+          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
+          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
+          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
+          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
+          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
+          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
+          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
+          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
+          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
+          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
+          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
+          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
+          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
+          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
+          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
+          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
+          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
+          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5edf6d865535d8fc</t>
+          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
+          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analyst Databricks</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
+          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Analyst Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
+          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>SRS Acquiom</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
+          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Science Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Site Reliability / DevOps Engineer</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>eClerx</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Event Hubs, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa7abd37eec3291</t>
+          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Data Science Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
+          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
+          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
+          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
+          <t>https://www.indeed.com/viewjob?jk=81ca06fa6ac3ac22</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>American Public Media</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer - Contingent</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>CRYOPORT SYSTEMS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Sr Software Developer - PEGA Platform</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ca06fa6ac3ac22</t>
+          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Ads Product &amp; Tech</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>American Public Media</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
+          <t>AWS, EMR, Azure, GCP, Dataflow, Hadoop, Scala, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
+          <t>https://www.indeed.com/viewjob?jk=59eacac00c3d239a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Contingent</t>
+          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CRYOPORT SYSTEMS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
+          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Software Developer - PEGA Platform</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Faro Health Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
+          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer, Ads Product &amp; Tech</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Dataflow, Hadoop, Scala, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59eacac00c3d239a</t>
+          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
+          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
+          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
+          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Concord, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Engineer (Core Engine)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
+          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
+          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
+          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
+          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
+          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
+          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
+          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
+          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
+          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer III Core Platform</t>
+          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
+          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Xai</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,59 +4871,59 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Xai</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
+          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Anaplan Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8de2684c6f92101f</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Anaplan Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de2684c6f92101f</t>
+          <t>https://www.indeed.com/viewjob?jk=513b06edfb3e0c5a</t>
         </is>
       </c>
     </row>
@@ -5438,17 +5438,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Software Engineer, Digital Engineering</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Vuori</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
+          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Digital Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Vuori</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,17 +5491,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
+          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
         </is>
       </c>
     </row>
@@ -5543,17 +5543,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
+          <t>https://www.indeed.com/viewjob?jk=cff67fb969376c22</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Web Application Engineer (Irvine, US)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Axon Networks</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78a4c688172469a</t>
+          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Payments</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3572e441b7b83887</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Security Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Network Engineer II</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Amerisure</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5710,41 +5710,6 @@
         </is>
       </c>
       <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Cloud Network Engineer II</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Amerisure</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Farmington Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98627ffbde1c523b</t>
         </is>

--- a/results/job_matches_2026-06-24.xlsx
+++ b/results/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,47 +1518,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Terraform)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98afda0b4cf6550d</t>
+          <t>https://www.indeed.com/viewjob?jk=c67ad259f5f7452d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Python Technical Specialist - Data Analysis, SQL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1567,38 +1567,38 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
+          <t>https://www.indeed.com/viewjob?jk=7208f4d9e700b7c7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>DevOps Engineer (Terraform)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
+          <t>https://www.indeed.com/viewjob?jk=98afda0b4cf6550d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1651,77 +1651,77 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Technical Architect</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rysun labs</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43d82f1543437048</t>
+          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
+          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
+          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
+          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
+          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
+          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
+          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
+          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
+          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
+          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
+          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
+          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
+          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
+          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
+          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
+          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
+          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
+          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
+          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
+          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
+          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
+          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
         </is>
       </c>
     </row>
@@ -3443,52 +3443,52 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
+          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Analyst Databricks</t>
+          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
+          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Analyst Databricks</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>Hilton Grand Vacations</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
+          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Dev.Ops</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>Liquidity Services, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e597d94585a188c3</t>
+          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Data Science Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SRS Acquiom</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Scala, Kafka, PostgreSQL, MySQL, ETL</t>
+          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,19 +3611,19 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45c1cc0f0a35f6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Data Science Engineer</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
+          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Architect – Capital Markets Domain</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MEDIIT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
+          <t>https://www.indeed.com/viewjob?jk=0df069435d852166</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,42 +3751,42 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Senior Data Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala, DataOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d633e19b2a078926</t>
+          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ca06fa6ac3ac22</t>
+          <t>https://www.indeed.com/viewjob?jk=9b737dc154be64ce</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>American Public Media</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, SQL Server, DynamoDB, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8390039bc78bb15</t>
+          <t>https://www.indeed.com/viewjob?jk=c416514550780a5b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Contingent</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CRYOPORT SYSTEMS</t>
+          <t>National Grid</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8dc6c2590850a50</t>
+          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Software Developer - PEGA Platform</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
+          <t>https://www.indeed.com/viewjob?jk=81ca06fa6ac3ac22</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer, Ads Product &amp; Tech</t>
+          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, GCP, Dataflow, Hadoop, Scala, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59eacac00c3d239a</t>
+          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
+          <t>Sr Software Developer - PEGA Platform</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
+          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Faro Health Inc.</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e75e8818d349ed7c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
+          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
+          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ERP Implementation Consultant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>MTC Corporation</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fountain Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7488931bef280ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=7270db5358b5fcdd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
+          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
         </is>
       </c>
     </row>
@@ -4253,55 +4253,55 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c0af65411f0014</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf87bc8d4644326b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff3e7b36fe0eff89</t>
+          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,67 +4381,67 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d3309aad7167c95</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af85de8b2a3ab880</t>
+          <t>https://www.indeed.com/viewjob?jk=c0edcab6ac0afe9c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff044df5cff76741</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Core Engine)</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=544039c92cd95980</t>
+          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
+          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Pratt Industries</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Park City, KS, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c94314064b7f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
+          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>Xai</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,102 +4626,102 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
+          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer III Core Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
+          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,59 +4766,59 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
+          <t>GCP Senior Data Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
+          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>MDM/DG SME/Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>PI Technologies LLC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
+          <t>https://www.indeed.com/viewjob?jk=869da5c5f350a735</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Platform Database Engineer (MONGO DB)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Xai</t>
+          <t>Valtech Group</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
+          <t>https://www.indeed.com/viewjob?jk=2103580026ffe43a</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
+          <t>https://www.indeed.com/viewjob?jk=513b06edfb3e0c5a</t>
         </is>
       </c>
     </row>
@@ -4918,12 +4918,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
+          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer - Austin, TX</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>Trend Micro Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Anaplan Architect</t>
+          <t>Engineer 2</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,67 +5046,67 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8de2684c6f92101f</t>
+          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>EMCOR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=513b06edfb3e0c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. Developer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>endava</t>
+          <t>829 Studios</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,94 +5116,94 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b23744e6c4bc494</t>
+          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
+          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Vectra AI</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Snowflake, PostgreSQL, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
+          <t>https://www.indeed.com/viewjob?jk=e361ec91914e9985</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Austin, TX</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Trend Micro Inc.</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Engineer 2</t>
+          <t>Sr. Software Engineer, Digital Engineering</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Vuori</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
+          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EMCOR</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>829 Studios</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8e26fb0df2e45c4d</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analyst, Audible People &amp; Places</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Cetera Financial Group</t>
+          <t>Audible</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Data Modeling, ETL, Amazon QuickSight, Power BI</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177f839eafc70423</t>
+          <t>https://www.indeed.com/viewjob?jk=c33bf2564ac4df12</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,29 +5386,29 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
+          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
+          <t>https://www.indeed.com/viewjob?jk=cff67fb969376c22</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Digital Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Vuori</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
+          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
         </is>
       </c>
     </row>
@@ -5513,12 +5513,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,182 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e26fb0df2e45c4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Curana Health</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cff67fb969376c22</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Ascendion</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Data Security Analyst</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Cloud Network Engineer II</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Amerisure</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Farmington Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98627ffbde1c523b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-24.xlsx
+++ b/results/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,25 +1063,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>HealthPartners</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ab6807d4d8842</t>
+          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,69 +1116,69 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea98351890cb41a5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Data Engineer - AWS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea98351890cb41a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9e78104b24dec2f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>Sr. Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,52 +1186,52 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e78104b24dec2f</t>
+          <t>https://www.indeed.com/viewjob?jk=849fb6429e007fcd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Development Operations - Archimedes</t>
+          <t>Data Engineer-Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849fb6429e007fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2fc4d359a22654</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
+          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack Data Science Engineer</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
+          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Data Architect – Capital Markets Domain</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>MEDIIT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=0df069435d852166</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect – Capital Markets Domain</t>
+          <t>Full Stack Data Science Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MEDIIT</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df069435d852166</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
         </is>
       </c>
     </row>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>iEnjoy Home</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, S3, Snowflake, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca154f0e79d5d8b7</t>
+          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
+          <t>SDE I- Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
+          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Software Developer - PEGA Platform</t>
+          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
+          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Sr Software Developer - PEGA Platform</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
+          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
+          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
+          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ERP Implementation Consultant</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MTC Corporation</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7270db5358b5fcdd</t>
+          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Development Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
         </is>
       </c>
     </row>
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
+          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0edcab6ac0afe9c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer III Core Platform</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
+          <t>https://www.indeed.com/viewjob?jk=c0edcab6ac0afe9c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
+          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Architect</t>
+          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Pratt Industries</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Park City, KS, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ba70a7ccef523f</t>
+          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2a5383caa636f90</t>
+          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Xai</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=162be4aca96e45e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
+          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
+          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>GCP Senior Data Architect</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>MDM/DG SME/Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>PI Technologies LLC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
+          <t>https://www.indeed.com/viewjob?jk=869da5c5f350a735</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GCP Senior Data Architect</t>
+          <t>Platform Database Engineer (MONGO DB)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Valtech Group</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
+          <t>https://www.indeed.com/viewjob?jk=2103580026ffe43a</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MDM/DG SME/Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PI Technologies LLC</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, ELT, Talend, Tableau</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869da5c5f350a735</t>
+          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Platform Database Engineer (MONGO DB)</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Valtech Group</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,112 +4861,112 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103580026ffe43a</t>
+          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer - Austin, TX</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Trend Micro Inc.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=513b06edfb3e0c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer 2</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
+          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>EMCOR</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Austin, TX</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Trend Micro Inc.</t>
+          <t>829 Studios</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Engineer 2</t>
+          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
+          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EMCOR</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>829 Studios</t>
+          <t>Vectra AI</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Snowflake, PostgreSQL, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e361ec91914e9985</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
+          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vectra AI</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Snowflake, PostgreSQL, MySQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e361ec91914e9985</t>
+          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
+          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform, SonarQube</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
+          <t>https://www.indeed.com/viewjob?jk=8e26fb0df2e45c4d</t>
         </is>
       </c>
     </row>
@@ -5263,17 +5263,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
+          <t>https://www.indeed.com/viewjob?jk=cff67fb969376c22</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e26fb0df2e45c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Analyst, Audible People &amp; Places</t>
+          <t>Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Audible</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Data Modeling, ETL, Amazon QuickSight, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c33bf2564ac4df12</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Security Analyst</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Amentum</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5430,111 +5430,6 @@
         </is>
       </c>
       <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cff67fb969376c22</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Ascendion</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Data Security Analyst</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Amentum</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
         </is>

--- a/results/job_matches_2026-06-24.xlsx
+++ b/results/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Development Operations - Archimedes</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>NinjaTrader</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,69 +1186,69 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
+          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, GCP, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849fb6429e007fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bde68b2f181a8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer-Adobe Exp Platform</t>
+          <t>Sr. Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2fc4d359a22654</t>
+          <t>https://www.indeed.com/viewjob?jk=849fb6429e007fcd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Data Engineer-Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2808323837e75ba</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2fc4d359a22654</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Azure, GCP, BigQuery, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=727cbe7cc2d8d727</t>
+          <t>https://www.indeed.com/viewjob?jk=f2808323837e75ba</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer – Insurance Data Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CCMSI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Danville, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d917a7b6e943564a</t>
+          <t>https://www.indeed.com/viewjob?jk=db60959b33c4c354</t>
         </is>
       </c>
     </row>
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db60959b33c4c354</t>
+          <t>https://www.indeed.com/viewjob?jk=bc118c13047230ec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Insurance Data Platform</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CCMSI</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Danville, IL, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc118c13047230ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f17df007528af5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>ClearpointCo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f17df007528af5</t>
+          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ClearpointCo</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
+          <t>https://www.indeed.com/viewjob?jk=c67ad259f5f7452d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Python Technical Specialist - Data Analysis, SQL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67ad259f5f7452d</t>
+          <t>https://www.indeed.com/viewjob?jk=7208f4d9e700b7c7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Python Technical Specialist - Data Analysis, SQL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7208f4d9e700b7c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Terraform)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98afda0b4cf6550d</t>
+          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,42 +3461,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Solutions Architect (AWS, Big Data, Data Engineering)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f3c602815dd894</t>
+          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Data Architect – Capital Markets Domain</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>MEDIIT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=0df069435d852166</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect – Capital Markets Domain</t>
+          <t>Full Stack Data Science Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MEDIIT</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df069435d852166</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Data Science Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
+          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
+          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>iEnjoy Home</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
+          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
         </is>
       </c>
     </row>
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b737dc154be64ce</t>
+          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>iEnjoy Home</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c416514550780a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e28d01d187be23b</t>
+          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
+          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
+          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
         </is>
       </c>
     </row>
@@ -4423,17 +4423,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Jonas Software</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0edcab6ac0afe9c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef996c4dca600f0c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer III Core Platform</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
+          <t>https://www.indeed.com/viewjob?jk=c0edcab6ac0afe9c</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Full Stack</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Purpose Financial</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, NoSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb8a3c0862e3915</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
+          <t>Sr. Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>Purpose Financial</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, ETL, CI/CD, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,42 +4556,42 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
+          <t>https://www.indeed.com/viewjob?jk=df13b44d139324c4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SQA Engineer – Data &amp; AI Platforms</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hive, Spark, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
+          <t>https://www.indeed.com/viewjob?jk=55b73c8351ce09fe</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
+          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>GCP Senior Data Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
+          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MDM/DG SME/Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PI Technologies LLC</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, ELT, Talend, Tableau</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869da5c5f350a735</t>
+          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Platform Database Engineer (MONGO DB)</t>
+          <t>GCP Senior Data Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Valtech Group</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103580026ffe43a</t>
+          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MDM/DG SME/Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>PI Technologies LLC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
+          <t>https://www.indeed.com/viewjob?jk=869da5c5f350a735</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Platform Database Engineer (MONGO DB)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Valtech Group</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,77 +4861,77 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
+          <t>https://www.indeed.com/viewjob?jk=2103580026ffe43a</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Austin, TX</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Trend Micro Inc.</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Engineer 2</t>
+          <t>Business Intelligence Architect / Developer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Navteca</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
+          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Cloud Platform Engineer II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EMCOR</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer - Austin, TX</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>829 Studios</t>
+          <t>Trend Micro Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, ETL, ELT, dbt, Tableau</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8312cf87c5ad3b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
+          <t>Engineer 2</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
+          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>EMCOR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Vectra AI</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Snowflake, PostgreSQL, MySQL, ELT, CI/CD</t>
+          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e361ec91914e9985</t>
+          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
+          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
+          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Terraform, SonarQube</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e26fb0df2e45c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Digital Engineering</t>
+          <t>Business Intelligence Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Vuori</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
+          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer, Digital Engineering</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>Vuori</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff67fb969376c22</t>
+          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, ETL, ELT, Talend, dbt</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8add5d2abfab0317</t>
+          <t>https://www.indeed.com/viewjob?jk=cff67fb969376c22</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Analytics and AI Developer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>Dexter Systems Inc</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
+          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Security Analyst</t>
+          <t>Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Amentum</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,17 +5386,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dd9d8654a0ed6a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
         </is>
       </c>
     </row>
@@ -5432,6 +5432,41 @@
       <c r="G143" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Product Engineer II - Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Esri</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Redlands, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, S3, SQS, RDS, Azure, Oracle, SQL Server, PostgreSQL, AWS CloudFormation, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4172ffc795a8a9ef</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-06-24.xlsx
+++ b/results/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Automation Developer &amp; Data Scientist</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.7</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, Data Factory, GCP, BigQuery</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8315a758255bb079</t>
+          <t>https://www.indeed.com/viewjob?jk=039085eefda4910b</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=039085eefda4910b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0ab289cd7fe039</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0ab289cd7fe039</t>
+          <t>https://www.indeed.com/viewjob?jk=419482d1afcd3dfa</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=419482d1afcd3dfa</t>
+          <t>https://www.indeed.com/viewjob?jk=d0e0aa784e6be257</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0e0aa784e6be257</t>
+          <t>https://www.indeed.com/viewjob?jk=161d68a146e54847</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=161d68a146e54847</t>
+          <t>https://www.indeed.com/viewjob?jk=de651327871de2a3</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive</t>
+          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de651327871de2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=10fc8879f0cc99f4</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fc8879f0cc99f4</t>
+          <t>https://www.indeed.com/viewjob?jk=bbb3b596dc7fb790</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbb3b596dc7fb790</t>
+          <t>https://www.indeed.com/viewjob?jk=f93edc3cecf59f63</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93edc3cecf59f63</t>
+          <t>https://www.indeed.com/viewjob?jk=19ea0d6a1b2e3218</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19ea0d6a1b2e3218</t>
+          <t>https://www.indeed.com/viewjob?jk=8809bbf8ab7927af</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809bbf8ab7927af</t>
+          <t>https://www.indeed.com/viewjob?jk=323c9080a1c5fd3c</t>
         </is>
       </c>
     </row>
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=323c9080a1c5fd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbeaab23e615686</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Python or GoLang Software Engineer - 2 days onsite (Chicago, IL) - FreeWheel</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,94 +1011,94 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, HBase</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, Azure, Databricks, GCP, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbeaab23e615686</t>
+          <t>https://www.indeed.com/viewjob?jk=2e805afd8491439b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Python or GoLang Software Engineer - 2 days onsite (Chicago, IL) - FreeWheel</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, Azure, Databricks, GCP, Spark</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e805afd8491439b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea98351890cb41a5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HealthPartners</t>
+          <t>NinjaTrader</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hive, Sqoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, GCP, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11738879dff288c</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bde68b2f181a8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Sr. Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,172 +1126,172 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea98351890cb41a5</t>
+          <t>https://www.indeed.com/viewjob?jk=849fb6429e007fcd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS</t>
+          <t>Data Engineer-Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9e78104b24dec2f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2fc4d359a22654</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AWS Cloud</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NinjaTrader</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Athena, S3, RDS, GCP, BigQuery, Cloud Storage</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bde68b2f181a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f2808323837e75ba</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Development Operations - Archimedes</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Scala, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849fb6429e007fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=2f587376655a4150</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer-Adobe Exp Platform</t>
+          <t>Senior Data Engineer – Insurance Data Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>CCMSI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Danville, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Google Cloud Platform, GCP, Hadoop, HDFS, Flume</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2fc4d359a22654</t>
+          <t>https://www.indeed.com/viewjob?jk=db60959b33c4c354</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Cloud</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>REI Systems</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,229 +1301,229 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2808323837e75ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f17df007528af5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>RDS, Azure, Data Factory, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f587376655a4150</t>
+          <t>https://www.indeed.com/viewjob?jk=c67ad259f5f7452d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Insurance Data Platform</t>
+          <t>Python Technical Specialist - Data Analysis, SQL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CCMSI</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Danville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
+          <t>AWS, Glue, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db60959b33c4c354</t>
+          <t>https://www.indeed.com/viewjob?jk=7208f4d9e700b7c7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Insurance Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CCMSI</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Danville, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, Databricks, Event Hubs, BigQuery, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc118c13047230ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>REI Systems</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, IAM, RDS, Scala, Oracle, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f17df007528af5</t>
+          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Engineer</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ClearpointCo</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, SQL Server</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d60eb49ba0667d</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Hadoop, Hive, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67ad259f5f7452d</t>
+          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Python Technical Specialist - Data Analysis, SQL</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1532,196 +1532,196 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7208f4d9e700b7c7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
+          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
+          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ELT, DataOps</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
+          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Project - Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
+          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f32c71c2e3662129</t>
+          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef84ae10230ce5</t>
+          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ae99da36b10a91f</t>
+          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43537078d05f52d7</t>
+          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500172c72664351c</t>
+          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db223ccd85851123</t>
+          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e365bb25b28383b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45ac0cea83dd4b59</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23bb86b7e4435095</t>
+          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9afd9bf6d062fb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb7336f0c30d74f</t>
+          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b32e77094fc38b3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0068341c421b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ca7c646de21592</t>
+          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73b69a1946f6cb7a</t>
+          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b52ccd3e5ef2d7</t>
+          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c3eca5ae1f3a135</t>
+          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106c2a749ba684d1</t>
+          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1702c469b845a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64f67e4a68fb0eb0</t>
+          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02768662d448cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18fc3e2e1eb7e56b</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Midland, MI, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c23c68d6476ca61</t>
+          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7a37890804c399</t>
+          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9236f6af20587bb8</t>
+          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ebdf6ceba2297</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccc4791b066386ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50fee0dffd0c3200</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14dd375c81fdeb91</t>
+          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43f1dc11c4fbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ad085e389cd274</t>
+          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb90114693a1860</t>
+          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Fresno, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec03f1c02e756ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9c4a54736321cbe</t>
+          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72febf5f9f66a41b</t>
+          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8691478fd49d352d</t>
+          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d805172dec7d7078</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Fresno, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b66de8fcf2854a1</t>
+          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=484812e5c48ae21b</t>
+          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338fa8ccf0de120a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a65983537d0239f</t>
+          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Karsun Solutions LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b36750075fd1b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44601ffec076b0c9</t>
+          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e7b426df8f6eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=97eae083068a3900</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe244724e210118</t>
+          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Project - Data Engineer</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Azure, Data Factory, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=848503ba4cc3d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Karsun Solutions LLC</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,54 +3366,54 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af06f826ddb18214</t>
+          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect – Capital Markets Domain</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>MEDIIT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff180e33e1711ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0df069435d852166</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Full Stack Data Science Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3422,108 +3422,108 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
+          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MongoDB, Cassandra, Data Modeling, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
+          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer, Data Integration - Archimedes</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
+          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Analyst Databricks</t>
+          <t>Sr. Engineer, Software - Archimedes</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hilton Grand Vacations</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,29 +3531,29 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c254b2804a86227c</t>
+          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Engineer II, Dev.Ops</t>
+          <t>Azure Senior Data Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Liquidity Services, Inc.</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3562,213 +3562,213 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala, DataOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=796db8b56cef3134</t>
+          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Architect – Capital Markets Domain</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MEDIIT</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df069435d852166</t>
+          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Data Science Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Databricks, BigQuery, Spark, Kafka, Snowflake, ELT, dbt, Power BI</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8c87a29c46c748</t>
+          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Engineer II, Data</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk</t>
+          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5790ca62d52326</t>
+          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Engineer, Data Integration - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>iEnjoy Home</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Kafka, ETL, ELT</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
+          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>National Grid</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
+          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Azure Senior Data Architect</t>
+          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, Hadoop, Spark, Scala, DataOps</t>
+          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
+          <t>https://www.indeed.com/viewjob?jk=81ca06fa6ac3ac22</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>SDE I- Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, MySQL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7731267ec6f619b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Kirkland, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db84cd672ebc6eb6</t>
+          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer II, Data</t>
+          <t>Sr Software Developer - PEGA Platform</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,52 +3881,52 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a73b9bce9a26b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>iEnjoy Home</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
+          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
         </is>
       </c>
     </row>
@@ -3938,55 +3938,55 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>EWC Corporate LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
+          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Engineer &amp; Data Architect, Financial Systems</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Salute Mission Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Oracle, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81ca06fa6ac3ac22</t>
+          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SDE I- Adobe Exp Platform</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
+          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineering AI Product Engineer (LLM Systems &amp; DevOps)</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kirkland, WA, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,137 +4066,137 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6785b8905e84e888</t>
+          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Software Developer - PEGA Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d03e70a1bdb46355</t>
+          <t>https://www.indeed.com/viewjob?jk=8ae211082b475d14</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Development Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14b20fe70c62919</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Salute Mission Inc.</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f913f3ad94b805</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Data Workflow Engineer – AI &amp; Automation Focus</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, Scala, NoSQL, Data Modeling, CI/CD, Jenkins, Terraform</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,59 +4206,59 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
+          <t>https://www.indeed.com/viewjob?jk=461aa75a8d591411</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e556b519575fbce1</t>
+          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer, Platform Engineering</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering Supervisor</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Texas Farm Bureau - Insurance Agents</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
+          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee927092c8f7b416</t>
+          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineering Supervisor</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Texas Farm Bureau - Insurance Agents</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d134831487c656</t>
+          <t>https://www.indeed.com/viewjob?jk=a53c3e01ff8163a0</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Space Communications)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, dbt, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b1cb6dc1b2a5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=0d634387249ab8ad</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer - Intern</t>
+          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jonas Software</t>
+          <t>OneMain Financial</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, IAM, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef996c4dca600f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0edcab6ac0afe9c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Observability &amp; Telemetry)</t>
+          <t>Software Engineer - Intern</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>OneMain Financial</t>
+          <t>Jonas Software</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Athena, S3, IAM, RDS, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0edcab6ac0afe9c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef996c4dca600f0c</t>
         </is>
       </c>
     </row>
@@ -4598,17 +4598,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Identity Security Engineer (SailPoint)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
+          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - Limited Tenure - Hybrid</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
+          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Devops</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
+          <t>Azure, Databricks, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
+          <t>https://www.indeed.com/viewjob?jk=6dec79ae33f75455</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>AWS, S3, IAM, Databricks, Spark, Scala, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
+          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Central Garden &amp; Pet</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b5702d9e6e218aec</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GCP Senior Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, ETL, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f7aabeaaea6b41</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MDM/DG SME/Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PI Technologies LLC</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, ELT, Talend, Tableau</t>
+          <t>Redshift, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=869da5c5f350a735</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Platform Database Engineer (MONGO DB)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Valtech Group</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, MongoDB, CI/CD, Terraform, Kubernetes</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2103580026ffe43a</t>
+          <t>https://www.indeed.com/viewjob?jk=66b66189499b2fbd</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Central Garden &amp; Pet</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Azure, Databricks, Unity Catalog, Scala, dbt, CI/CD, GitHub Actions, Azure DevOps, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf83e74216973df</t>
+          <t>https://www.indeed.com/viewjob?jk=28d4e6eca38676f5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect / Developer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Navteca</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,42 +4931,42 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a903253fe750059f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe70c0ae09b9a043</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer II</t>
+          <t>GCP Senior Data Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, DataOps</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,129 +4976,129 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
+          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Austin, TX</t>
+          <t>MDM/DG SME/Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Trend Micro Inc.</t>
+          <t>PI Technologies LLC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
+          <t>https://www.indeed.com/viewjob?jk=869da5c5f350a735</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Engineer 2</t>
+          <t>Platform Database Engineer (MONGO DB)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Valtech Group</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, MongoDB, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
+          <t>https://www.indeed.com/viewjob?jk=2103580026ffe43a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>ForgeRock Federation Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EMCOR</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tonawanda, NY, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, REST API integration, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=1df9b945be5959e8</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Java Cloud Migration Engineer (OpenShift / Infrastructure &amp; Application Modernization)</t>
+          <t>DataOS Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, dbt, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63f649b6edb613b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ae32622f84d5fcf</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Cloud Platform Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e33085bec67c090e</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Senior Data Engineer - Austin, TX</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Trend Micro Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
+          <t>https://www.indeed.com/viewjob?jk=8f2319340732e3c2</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Engineer 2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
+          <t>https://www.indeed.com/viewjob?jk=6936a8a4f52ab947</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>EMCOR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tonawanda, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33584297ea5a4c</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Digital Engineering</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vuori</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
+          <t>https://www.indeed.com/viewjob?jk=402264050a42b554</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Curana Health</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff67fb969376c22</t>
+          <t>https://www.indeed.com/viewjob?jk=c2876f4244aa1e51</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Business Intelligence Engineer II</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dexter Systems Inc</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
+          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Analytics and AI Developer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
+          <t>https://www.indeed.com/viewjob?jk=69a2a743f46a4e4c</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer, Digital Engineering</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Vuori</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
+          <t>https://www.indeed.com/viewjob?jk=874d1c8eb2f55d75</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Product Engineer II - Cloud Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Curana Health</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,15 +5456,190 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cff67fb969376c22</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Data Warehouse Developer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Dexter Systems Inc</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Kimball, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=740c65f047ff500a</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Analytics and AI Developer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Rochester Electronics</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Newburyport, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57316bd44c07be7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Python Developer II</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Finance of America</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, Scala, PostgreSQL, Docker, Kubernetes, pytest, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21327b99c0a351e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Product Engineer II - Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Esri</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Redlands, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
           <t>AWS, S3, SQS, RDS, Azure, Oracle, SQL Server, PostgreSQL, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4172ffc795a8a9ef</t>
         </is>
